--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484649_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484649_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.894399999999999</v>
+        <v>9.3696</v>
       </c>
       <c r="E2" t="n">
-        <v>9.568199999999999</v>
+        <v>9.1424</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3263</v>
+        <v>0.2272</v>
       </c>
       <c r="G2" t="n">
         <v>4.2223</v>
@@ -610,13 +610,13 @@
         <v>1.8326</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6934</v>
+        <v>1.1685</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9329</v>
+        <v>0.5072</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7605</v>
+        <v>0.6614</v>
       </c>
       <c r="V2" t="n">
         <v>5.0783</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7492</v>
+        <v>5.9366</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8024</v>
+        <v>4.8163</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9469</v>
+        <v>1.1203</v>
       </c>
       <c r="G3" t="n">
         <v>3.1886</v>
@@ -688,13 +688,13 @@
         <v>1.8326</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2333</v>
+        <v>1.4206</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8778</v>
+        <v>0.8918</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3554</v>
+        <v>0.5288</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3219</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.4406</v>
+        <v>5.8437</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3425</v>
+        <v>3.1668</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0981</v>
+        <v>2.6769</v>
       </c>
       <c r="G4" t="n">
         <v>1.4175</v>
@@ -766,13 +766,13 @@
         <v>2.5656</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9681</v>
+        <v>1.3712</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4593</v>
+        <v>0.365</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4273</v>
+        <v>1.0062</v>
       </c>
       <c r="V4" t="n">
         <v>1.5889</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.8579</v>
+        <v>5.5016</v>
       </c>
       <c r="E5" t="n">
-        <v>2.712</v>
+        <v>2.9594</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1458</v>
+        <v>2.5422</v>
       </c>
       <c r="G5" t="n">
         <v>3.2906</v>
@@ -844,13 +844,13 @@
         <v>1.4661</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3736</v>
+        <v>1.0173</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2187</v>
+        <v>0.4661</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1549</v>
+        <v>0.5513</v>
       </c>
       <c r="V5" t="n">
         <v>0.6439</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.0495</v>
+        <v>3.78</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8828</v>
+        <v>2.7866</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1668</v>
+        <v>0.9933999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>3.7554</v>
@@ -922,13 +922,13 @@
         <v>0.9163</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2599</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.457</v>
+        <v>0.3609</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8028999999999999</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>-0.9658</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.4651</v>
+        <v>3.3441</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6282</v>
+        <v>1.5321</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8369</v>
+        <v>1.8121</v>
       </c>
       <c r="G7" t="n">
         <v>3.0229</v>
@@ -1000,13 +1000,13 @@
         <v>1.0995</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5521</v>
+        <v>0.4312</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6041</v>
+        <v>0.5079</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.052</v>
+        <v>-0.0767</v>
       </c>
       <c r="V7" t="n">
         <v>0.6231</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.5468</v>
+        <v>2.1022</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8136</v>
+        <v>1.1956</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7332</v>
+        <v>0.9067</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0522</v>
@@ -1078,13 +1078,13 @@
         <v>1.0995</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4158</v>
+        <v>0.9712</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0249</v>
+        <v>0.4069</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3909</v>
+        <v>0.5643</v>
       </c>
       <c r="V8" t="n">
         <v>1.267</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6362</v>
+        <v>1.2594</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3433</v>
+        <v>0.5772</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9794</v>
+        <v>0.6822</v>
       </c>
       <c r="G9" t="n">
         <v>2.7748</v>
@@ -1156,13 +1156,13 @@
         <v>0.9163</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6102</v>
+        <v>1.2334</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4042</v>
+        <v>0.5162</v>
       </c>
       <c r="U9" t="n">
-        <v>1.0144</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. SAEZ GONZALEZ</t>
+          <t>I. ALONSO QUINZA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1325</v>
+        <v>0.1705</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1127</v>
+        <v>0.9663</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2452</v>
+        <v>-0.7958</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3851</v>
+        <v>0.0501</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1116</v>
+        <v>-2.505</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4968</v>
+        <v>2.5552</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5011</v>
+        <v>1.4241</v>
       </c>
       <c r="K10" t="n">
-        <v>0.13</v>
+        <v>-1.1954</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6312</v>
+        <v>2.6194</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.884</v>
+        <v>-1.3739</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0184</v>
+        <v>-1.3097</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8656</v>
+        <v>-0.0643</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9163</v>
+        <v>-1.0995</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9163</v>
+        <v>0.1833</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5746</v>
+        <v>0.0916</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2082</v>
+        <v>0.0083</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3664</v>
+        <v>0.0833</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3219</v>
+        <v>0.945</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3219</v>
+        <v>0.6335</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6439</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. ALONSO QUINZA</t>
+          <t>A. BULDU IZQUIERDO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3246</v>
+        <v>-0.1885</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7189</v>
+        <v>2.1825</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0435</v>
+        <v>-2.371</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0501</v>
+        <v>1.4852</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.505</v>
+        <v>1.3923</v>
       </c>
       <c r="I11" t="n">
-        <v>2.5552</v>
+        <v>0.0929</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4241</v>
+        <v>3.1811</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.1954</v>
+        <v>3.0561</v>
       </c>
       <c r="L11" t="n">
-        <v>2.6194</v>
+        <v>0.125</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3739</v>
+        <v>-1.6959</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3097</v>
+        <v>-1.6638</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0643</v>
+        <v>-0.0321</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9163</v>
+        <v>-1.6493</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0995</v>
+        <v>-1.8326</v>
       </c>
       <c r="R11" t="n">
         <v>0.1833</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4035</v>
+        <v>0.6092</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2391</v>
+        <v>0.5121</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1644</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>0.945</v>
+        <v>-0.6335</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6335</v>
+        <v>0.3219</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3115</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3773</v>
+        <v>-0.5448</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6462</v>
+        <v>0.4539</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0235</v>
+        <v>-0.9988</v>
       </c>
       <c r="G12" t="n">
         <v>-1.6134</v>
@@ -1390,13 +1390,13 @@
         <v>0.733</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4743</v>
+        <v>0.3068</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4389</v>
+        <v>0.2466</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0354</v>
+        <v>0.0601</v>
       </c>
       <c r="V12" t="n">
         <v>0.945</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. BULDU IZQUIERDO</t>
+          <t>J. SAEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.4665</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1275</v>
+        <v>-0.2169</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.594</v>
+        <v>-0.4682</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4852</v>
+        <v>-1.3851</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3923</v>
+        <v>0.1116</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0929</v>
+        <v>-1.4968</v>
       </c>
       <c r="J13" t="n">
-        <v>3.1811</v>
+        <v>-0.5011</v>
       </c>
       <c r="K13" t="n">
-        <v>3.0561</v>
+        <v>0.13</v>
       </c>
       <c r="L13" t="n">
-        <v>0.125</v>
+        <v>-0.6312</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.6959</v>
+        <v>-0.884</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.6638</v>
+        <v>-0.0184</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0321</v>
+        <v>-0.8656</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.6493</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1833</v>
+        <v>0.9163</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3312</v>
+        <v>1.0221</v>
       </c>
       <c r="T13" t="n">
-        <v>0.457</v>
+        <v>0.8786</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1259</v>
+        <v>0.1435</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.6335</v>
+        <v>-0.3219</v>
       </c>
       <c r="W13" t="n">
         <v>0.3219</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.9554</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>35.3388</v>
+        <v>35.88939999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>29.0117</v>
+        <v>29.5622</v>
       </c>
       <c r="F14" t="n">
-        <v>6.327199999999999</v>
+        <v>6.327199999999998</v>
       </c>
       <c r="G14" t="n">
         <v>19.1567</v>
@@ -1528,7 +1528,7 @@
         <v>6.573700000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-6.619199999999999</v>
+        <v>-6.6192</v>
       </c>
       <c r="N14" t="n">
         <v>-11.9065</v>
@@ -1546,16 +1546,16 @@
         <v>13.7444</v>
       </c>
       <c r="S14" t="n">
-        <v>10.083</v>
+        <v>10.6335</v>
       </c>
       <c r="T14" t="n">
-        <v>5.1169</v>
+        <v>5.6676</v>
       </c>
       <c r="U14" t="n">
-        <v>4.965800000000001</v>
+        <v>4.966000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>8.848099999999999</v>
+        <v>8.848100000000001</v>
       </c>
       <c r="W14" t="n">
         <v>14.6118</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1099</v>
+        <v>1.7762</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6904</v>
+        <v>2.4019</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5805</v>
+        <v>-0.6257</v>
       </c>
       <c r="G15" t="n">
         <v>0.5819</v>
@@ -1624,13 +1624,13 @@
         <v>2.1991</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2076</v>
+        <v>-0.5413</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2036</v>
+        <v>-0.4921</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.004</v>
+        <v>-0.0492</v>
       </c>
       <c r="V15" t="n">
         <v>0.4528</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7946</v>
+        <v>1.0758</v>
       </c>
       <c r="E17" t="n">
         <v>0.7422</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0523</v>
+        <v>0.3335</v>
       </c>
       <c r="G17" t="n">
         <v>0.1448</v>
@@ -1780,13 +1780,13 @@
         <v>1.0995</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5702</v>
+        <v>-0.289</v>
       </c>
       <c r="T17" t="n">
         <v>-0.4774</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.09279999999999999</v>
+        <v>0.1883</v>
       </c>
       <c r="V17" t="n">
         <v>0.1205</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5031</v>
+        <v>-0.4317</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.003</v>
+        <v>-0.2914</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5002</v>
+        <v>-0.1403</v>
       </c>
       <c r="G18" t="n">
         <v>-0.138</v>
@@ -1858,13 +1858,13 @@
         <v>1.8326</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7684</v>
+        <v>-0.697</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.3639</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-0.3332</v>
       </c>
       <c r="V18" t="n">
         <v>-0.513</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. VIVES HURTADO</t>
+          <t>M. GONZALEZ MAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2717</v>
+        <v>-1.0874</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2676</v>
+        <v>-0.6039</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5392</v>
+        <v>-0.4835</v>
       </c>
       <c r="G19" t="n">
-        <v>0.07240000000000001</v>
+        <v>-1.3072</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7134</v>
+        <v>-0.6341</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.641</v>
+        <v>-0.6732</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3777</v>
+        <v>-0.576</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0187</v>
+        <v>0.065</v>
       </c>
       <c r="L19" t="n">
         <v>-0.641</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3053</v>
+        <v>-0.7312</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3053</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-0.0321</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.5498</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.5498</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0771</v>
+        <v>-0.3299</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1101</v>
+        <v>-0.0279</v>
       </c>
       <c r="U19" t="n">
-        <v>0.033</v>
+        <v>-0.302</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. GONZALEZ MAS</t>
+          <t>A. VIVES HURTADO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4575</v>
+        <v>-1.2221</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7962</v>
+        <v>0.2676</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6612</v>
+        <v>-1.4897</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.3072</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6341</v>
+        <v>0.7134</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6732</v>
+        <v>-0.641</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.576</v>
+        <v>0.3777</v>
       </c>
       <c r="K20" t="n">
-        <v>0.065</v>
+        <v>1.0187</v>
       </c>
       <c r="L20" t="n">
         <v>-0.641</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7312</v>
+        <v>-0.3053</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6991000000000001</v>
+        <v>-0.3053</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0321</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5498</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5498</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7</v>
+        <v>-0.0275</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2202</v>
+        <v>-0.1101</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4798</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1865</v>
+        <v>-3.3745</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1345</v>
+        <v>-0.3269</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.052</v>
+        <v>-3.0477</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8602</v>
@@ -2092,13 +2092,13 @@
         <v>2.1991</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8707</v>
+        <v>-1.0586</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4419</v>
+        <v>-0.6342</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4288</v>
+        <v>-0.4244</v>
       </c>
       <c r="V21" t="n">
         <v>0.0104</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. ESTARLICH MARTINEZ</t>
+          <t>M. SHALABI TORRES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5311</v>
+        <v>-3.3933</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2269</v>
+        <v>-0.4433</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.758</v>
+        <v>-2.95</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.6756</v>
+        <v>-3.6065</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5363</v>
+        <v>-0.0775</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.2119</v>
+        <v>-3.529</v>
       </c>
       <c r="J22" t="n">
-        <v>2.3468</v>
+        <v>-0.7869</v>
       </c>
       <c r="K22" t="n">
-        <v>3.6288</v>
+        <v>2.3251</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2821</v>
+        <v>-3.1119</v>
       </c>
       <c r="M22" t="n">
-        <v>-4.0223</v>
+        <v>-2.8196</v>
       </c>
       <c r="N22" t="n">
-        <v>-3.0925</v>
+        <v>-2.4026</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.417</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5498</v>
+        <v>2.3823</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4661</v>
+        <v>2.3823</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8164</v>
+        <v>-1.0226</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2036</v>
+        <v>-0.9234</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6128</v>
+        <v>-0.0992</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.5889</v>
+        <v>-1.1465</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.5889</v>
+        <v>-2.4135</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. SHALABI TORRES</t>
+          <t>J. ESTARLICH MARTINEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3141</v>
+        <v>-3.4713</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7318</v>
+        <v>1.0346</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.5823</v>
+        <v>-4.5059</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.6065</v>
+        <v>-1.6756</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0775</v>
+        <v>0.5363</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.529</v>
+        <v>-2.2119</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7869</v>
+        <v>2.3468</v>
       </c>
       <c r="K23" t="n">
-        <v>2.3251</v>
+        <v>3.6288</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.1119</v>
+        <v>-1.2821</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.8196</v>
+        <v>-4.0223</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.4026</v>
+        <v>-3.0925</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.417</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>2.3823</v>
+        <v>0.5498</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3823</v>
+        <v>1.4661</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.9434</v>
+        <v>-0.7566000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2119</v>
+        <v>-0.3959</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7315</v>
+        <v>-0.3607</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.1465</v>
+        <v>-1.5889</v>
       </c>
       <c r="W23" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.4135</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.3548</v>
+        <v>-3.6788</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.3734</v>
+        <v>-0.1811</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.9814</v>
+        <v>-3.4977</v>
       </c>
       <c r="G24" t="n">
         <v>-2.0093</v>
@@ -2326,13 +2326,13 @@
         <v>1.0995</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0523</v>
+        <v>-0.3763</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6244</v>
+        <v>-0.4321</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4279</v>
+        <v>0.0558</v>
       </c>
       <c r="V24" t="n">
         <v>-2.3927</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.0354</v>
+        <v>-4.7529</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.1301</v>
+        <v>-3.0339</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.9054</v>
+        <v>-1.719</v>
       </c>
       <c r="G25" t="n">
         <v>-2.7705</v>
@@ -2404,13 +2404,13 @@
         <v>0.9163</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7543</v>
+        <v>-0.4717</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4774</v>
+        <v>-0.3812</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2769</v>
+        <v>-0.0905</v>
       </c>
       <c r="V25" t="n">
         <v>0.3219</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.5834</v>
+        <v>-5.5761</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.4289</v>
+        <v>-2.525</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.1545</v>
+        <v>-3.0511</v>
       </c>
       <c r="G26" t="n">
         <v>-4.7494</v>
@@ -2482,13 +2482,13 @@
         <v>1.4661</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.0618</v>
+        <v>-1.0545</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2405</v>
+        <v>-0.3367</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.8212</v>
+        <v>-0.7178</v>
       </c>
       <c r="V26" t="n">
         <v>-0.3219</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-10.3063</v>
+        <v>-9.9392</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.9568</v>
+        <v>-4.6684</v>
       </c>
       <c r="F27" t="n">
-        <v>-5.3495</v>
+        <v>-5.2708</v>
       </c>
       <c r="G27" t="n">
         <v>-4.1397</v>
@@ -2560,13 +2560,13 @@
         <v>1.2828</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.2608</v>
+        <v>-0.8937</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.6795</v>
+        <v>-0.391</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.5813</v>
+        <v>-0.5027</v>
       </c>
       <c r="V27" t="n">
         <v>-2.5235</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-35.3389</v>
+        <v>-32.7748</v>
       </c>
       <c r="E28" t="n">
         <v>-6.3271</v>
       </c>
       <c r="F28" t="n">
-        <v>-29.0119</v>
+        <v>-26.4479</v>
       </c>
       <c r="G28" t="n">
         <v>-19.1568</v>
@@ -2611,7 +2611,7 @@
         <v>-11.8613</v>
       </c>
       <c r="J28" t="n">
-        <v>6.619300000000001</v>
+        <v>6.619299999999999</v>
       </c>
       <c r="K28" t="n">
         <v>11.9067</v>
@@ -2638,13 +2638,13 @@
         <v>16.4932</v>
       </c>
       <c r="S28" t="n">
-        <v>-10.083</v>
+        <v>-7.5187</v>
       </c>
       <c r="T28" t="n">
         <v>-4.9659</v>
       </c>
       <c r="U28" t="n">
-        <v>-5.117</v>
+        <v>-2.553</v>
       </c>
       <c r="V28" t="n">
         <v>-8.847900000000001</v>
